--- a/cet4/result/46_医道女神_白衣天使的奇迹/46_医道女神_白衣天使的奇迹_学习版.xlsx
+++ b/cet4/result/46_医道女神_白衣天使的奇迹/46_医道女神_白衣天使的奇迹_学习版.xlsx
@@ -397,787 +397,703 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D49"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>snow</v>
       </c>
       <c r="B2" t="str">
-        <v>snow</v>
+        <v>/snoʊ/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D2" t="str">
         <v>雪</v>
       </c>
-      <c r="D2" t="str">
-        <v>snow(雪)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>camera</v>
       </c>
       <c r="B3" t="str">
-        <v>camera</v>
+        <v>/ˈkæmrə/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>摄像头</v>
       </c>
-      <c r="D3" t="str">
-        <v>camera(摄像头)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>adopt</v>
       </c>
       <c r="B4" t="str">
-        <v>adopt</v>
+        <v>/əˈdɑːpt/</v>
       </c>
       <c r="C4" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D4" t="str">
         <v>采取</v>
       </c>
-      <c r="D4" t="str">
-        <v>adopt(采取)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>daughter</v>
       </c>
       <c r="B5" t="str">
-        <v>daughter</v>
+        <v>/ˈdɔːtər/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>女儿</v>
       </c>
-      <c r="D5" t="str">
-        <v>daughter(女儿)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>hate</v>
       </c>
       <c r="B6" t="str">
-        <v>hate</v>
+        <v>/heɪt/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D6" t="str">
         <v>恨意</v>
       </c>
-      <c r="D6" t="str">
-        <v>hate(恨意)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>serious</v>
       </c>
       <c r="B7" t="str">
-        <v>serious</v>
+        <v>/ˈsɪriəs/</v>
       </c>
       <c r="C7" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D7" t="str">
         <v>严重</v>
       </c>
-      <c r="D7" t="str">
-        <v>serious(严重)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>neck</v>
       </c>
       <c r="B8" t="str">
-        <v>neck</v>
+        <v>/nek/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D8" t="str">
         <v>颈</v>
       </c>
-      <c r="D8" t="str">
-        <v>neck(颈)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>ounce</v>
       </c>
       <c r="B9" t="str">
-        <v>ounce</v>
+        <v>/aʊns/</v>
       </c>
       <c r="C9" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>盎司</v>
       </c>
-      <c r="D9" t="str">
-        <v>ounce(盎司)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>understanding</v>
       </c>
       <c r="B10" t="str">
-        <v>understanding</v>
+        <v>/ˌʌndərˈstændɪŋ/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./v./adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>理解</v>
       </c>
-      <c r="D10" t="str">
-        <v>understanding(理解)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>sharp</v>
       </c>
       <c r="B11" t="str">
-        <v>sharp</v>
+        <v>/ʃɑːrp/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./vt./vi./v./adj./adv.</v>
+      </c>
+      <c r="D11" t="str">
         <v>敏锐</v>
       </c>
-      <c r="D11" t="str">
-        <v>sharp(敏锐)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>mortal</v>
       </c>
       <c r="B12" t="str">
-        <v>mortal</v>
+        <v>/ˈmɔːrtl/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>凡人/致命的</v>
       </c>
-      <c r="D12" t="str">
-        <v>mortal(凡人/致命的)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>harness</v>
       </c>
       <c r="B13" t="str">
-        <v>harness</v>
+        <v>/ˈhɑːrnɪs/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D13" t="str">
         <v>利用</v>
       </c>
-      <c r="D13" t="str">
-        <v>harness(利用)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>loyal</v>
       </c>
       <c r="B14" t="str">
-        <v>loyal</v>
+        <v>/ˈlɔɪəl/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>忠诚的</v>
       </c>
-      <c r="D14" t="str">
-        <v>loyal(忠诚的)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>possible</v>
       </c>
       <c r="B15" t="str">
-        <v>possible</v>
+        <v>/ˈpɑːsəbl/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D15" t="str">
         <v>可能的</v>
       </c>
-      <c r="D15" t="str">
-        <v>possible(可能的)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>explode</v>
       </c>
       <c r="B16" t="str">
-        <v>explode</v>
+        <v>/ɪkˈsploʊd/</v>
       </c>
       <c r="C16" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D16" t="str">
         <v>爆炸/爆发</v>
       </c>
-      <c r="D16" t="str">
-        <v>explode(爆炸/爆发)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>afterward</v>
       </c>
       <c r="B17" t="str">
-        <v>afterward</v>
+        <v>/ˈæftərwərd/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D17" t="str">
         <v>后来</v>
       </c>
-      <c r="D17" t="str">
-        <v>afterward(后来)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>seat</v>
       </c>
       <c r="B18" t="str">
-        <v>seat</v>
+        <v>/siːt/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D18" t="str">
         <v>座位</v>
       </c>
-      <c r="D18" t="str">
-        <v>seat(座位)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>sleeve</v>
       </c>
       <c r="B19" t="str">
-        <v>sleeve</v>
+        <v>/sliːv/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D19" t="str">
         <v>袖子</v>
       </c>
-      <c r="D19" t="str">
-        <v>sleeve(袖子)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>timetable</v>
       </c>
       <c r="B20" t="str">
-        <v>timetable</v>
+        <v>/ˈtaɪmteɪbl/</v>
       </c>
       <c r="C20" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>时间表</v>
       </c>
-      <c r="D20" t="str">
-        <v>timetable(时间表)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>thing</v>
       </c>
       <c r="B21" t="str">
-        <v>thing</v>
+        <v>/θɪŋ/</v>
       </c>
       <c r="C21" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>事情</v>
       </c>
-      <c r="D21" t="str">
-        <v>thing(事情)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>leave</v>
       </c>
       <c r="B22" t="str">
-        <v>leave</v>
+        <v>/liːv/</v>
       </c>
       <c r="C22" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D22" t="str">
         <v>离开</v>
       </c>
-      <c r="D22" t="str">
-        <v>leave(离开)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>discharge</v>
       </c>
       <c r="B23" t="str">
-        <v>discharge</v>
+        <v>/dɪsˈtʃɑːrdʒ/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D23" t="str">
         <v>出院</v>
       </c>
-      <c r="D23" t="str">
-        <v>discharge(出院)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>ribbon</v>
       </c>
       <c r="B24" t="str">
-        <v>ribbon</v>
+        <v>/ˈrɪbən/</v>
       </c>
       <c r="C24" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D24" t="str">
         <v>丝带</v>
       </c>
-      <c r="D24" t="str">
-        <v>ribbon(丝带)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>trifle</v>
       </c>
       <c r="B25" t="str">
-        <v>trifle</v>
+        <v>/ˈtraɪfl/</v>
       </c>
       <c r="C25" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D25" t="str">
         <v>小事</v>
       </c>
-      <c r="D25" t="str">
-        <v>trifle(小事)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>money</v>
       </c>
       <c r="B26" t="str">
-        <v>money</v>
+        <v>/ˈmʌni/</v>
       </c>
       <c r="C26" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>金钱</v>
       </c>
-      <c r="D26" t="str">
-        <v>money(金钱)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>ancient</v>
       </c>
       <c r="B27" t="str">
-        <v>ancient</v>
+        <v>/ˈeɪnʃənt/</v>
       </c>
       <c r="C27" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D27" t="str">
         <v>古老的</v>
       </c>
-      <c r="D27" t="str">
-        <v>ancient(古老的)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>flower</v>
       </c>
       <c r="B28" t="str">
-        <v>flower</v>
+        <v>/ˈflaʊər/</v>
       </c>
       <c r="C28" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D28" t="str">
         <v>花</v>
       </c>
-      <c r="D28" t="str">
-        <v>flower(花)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>chalk</v>
       </c>
       <c r="B29" t="str">
-        <v>mortal</v>
+        <v>/tʃɔːk/</v>
       </c>
       <c r="C29" t="str">
-        <v>凡人</v>
+        <v>n./vt.</v>
       </c>
       <c r="D29" t="str">
-        <v>mortal(凡人)📢</v>
+        <v>粉笔</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>essay</v>
       </c>
       <c r="B30" t="str">
-        <v>chalk</v>
+        <v>/ˈeseɪ/</v>
       </c>
       <c r="C30" t="str">
-        <v>粉笔</v>
+        <v>n./vt.</v>
       </c>
       <c r="D30" t="str">
-        <v>chalk(粉笔)📢</v>
+        <v>文章</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>pretend</v>
       </c>
       <c r="B31" t="str">
-        <v>essay</v>
+        <v>/prɪˈtend/</v>
       </c>
       <c r="C31" t="str">
-        <v>文章</v>
+        <v>vt./vi./adj.</v>
       </c>
       <c r="D31" t="str">
-        <v>essay(文章)📢</v>
+        <v>假装</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>dying</v>
       </c>
       <c r="B32" t="str">
-        <v>pretend</v>
+        <v>/ˈdaɪɪŋ/</v>
       </c>
       <c r="C32" t="str">
-        <v>假装</v>
+        <v>adj.</v>
       </c>
       <c r="D32" t="str">
-        <v>pretend(假装)📢</v>
+        <v>垂死的</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>cure</v>
       </c>
       <c r="B33" t="str">
-        <v>dying</v>
+        <v>/kjʊr/</v>
       </c>
       <c r="C33" t="str">
-        <v>垂死的</v>
+        <v>n./v.</v>
       </c>
       <c r="D33" t="str">
-        <v>dying(垂死的)📢</v>
+        <v>治愈</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>cooperate</v>
       </c>
       <c r="B34" t="str">
-        <v>cure</v>
+        <v>/koʊˈɑːpəreɪt/</v>
       </c>
       <c r="C34" t="str">
-        <v>治愈</v>
+        <v>vi.</v>
       </c>
       <c r="D34" t="str">
-        <v>cure(治愈)📢</v>
+        <v>合作</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>victorious</v>
       </c>
       <c r="B35" t="str">
-        <v>cooperate</v>
+        <v>/vɪkˈtɔːriəs/</v>
       </c>
       <c r="C35" t="str">
-        <v>合作</v>
+        <v>adj.</v>
       </c>
       <c r="D35" t="str">
-        <v>cooperate(合作)📢</v>
+        <v>胜利的</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>big</v>
       </c>
       <c r="B36" t="str">
-        <v>victorious</v>
+        <v>/bɪɡ/</v>
       </c>
       <c r="C36" t="str">
-        <v>胜利的</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D36" t="str">
-        <v>victorious(胜利的)📢</v>
+        <v>大的</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>exploit</v>
       </c>
       <c r="B37" t="str">
-        <v>big</v>
+        <v>/ɪkˈsplɔɪt/</v>
       </c>
       <c r="C37" t="str">
-        <v>大的</v>
+        <v>n./vt.</v>
       </c>
       <c r="D37" t="str">
-        <v>big(大的)📢</v>
+        <v>利用/开发</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>simplify</v>
       </c>
       <c r="B38" t="str">
-        <v>exploit</v>
+        <v>/ˈsɪmplɪfaɪ/</v>
       </c>
       <c r="C38" t="str">
-        <v>利用/开发</v>
+        <v>vt.</v>
       </c>
       <c r="D38" t="str">
-        <v>exploit(利用/开发)📢</v>
+        <v>简化</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>breadth</v>
       </c>
       <c r="B39" t="str">
-        <v>simplify</v>
+        <v>/bredθ/</v>
       </c>
       <c r="C39" t="str">
-        <v>简化</v>
+        <v>n.</v>
       </c>
       <c r="D39" t="str">
-        <v>simplify(简化)📢</v>
+        <v>宽度</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>zone</v>
       </c>
       <c r="B40" t="str">
-        <v>breadth</v>
+        <v>/zoʊn/</v>
       </c>
       <c r="C40" t="str">
-        <v>宽度</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D40" t="str">
-        <v>breadth(宽度)📢</v>
+        <v>区域</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>result</v>
       </c>
       <c r="B41" t="str">
-        <v>zone</v>
+        <v>/rɪˈzʌlt/</v>
       </c>
       <c r="C41" t="str">
-        <v>区域</v>
+        <v>n./vi.</v>
       </c>
       <c r="D41" t="str">
-        <v>zone(区域)📢</v>
+        <v>结果</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>sole</v>
       </c>
       <c r="B42" t="str">
-        <v>result</v>
+        <v>/soʊl/</v>
       </c>
       <c r="C42" t="str">
-        <v>结果</v>
+        <v>n./v./adj.</v>
       </c>
       <c r="D42" t="str">
-        <v>result(结果)📢</v>
+        <v>唯一的</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>still</v>
       </c>
       <c r="B43" t="str">
-        <v>sole</v>
+        <v>/stɪl/</v>
       </c>
       <c r="C43" t="str">
-        <v>唯一的</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D43" t="str">
-        <v>sole(唯一的)📢</v>
+        <v>静止的</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>rake</v>
       </c>
       <c r="B44" t="str">
-        <v>still</v>
+        <v>/reɪk/</v>
       </c>
       <c r="C44" t="str">
-        <v>静止的</v>
+        <v>n./v.</v>
       </c>
       <c r="D44" t="str">
-        <v>still(静止的)📢</v>
+        <v>耙子</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>tell</v>
       </c>
       <c r="B45" t="str">
-        <v>rake</v>
+        <v>/tel/</v>
       </c>
       <c r="C45" t="str">
-        <v>耙子</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D45" t="str">
-        <v>rake(耙子)📢</v>
+        <v>告诉</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>hold</v>
       </c>
       <c r="B46" t="str">
-        <v>tell</v>
+        <v>/hoʊld/</v>
       </c>
       <c r="C46" t="str">
-        <v>告诉</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D46" t="str">
-        <v>tell(告诉)📢</v>
+        <v>保持</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>mix</v>
       </c>
       <c r="B47" t="str">
-        <v>hold</v>
+        <v>/mɪks/</v>
       </c>
       <c r="C47" t="str">
-        <v>保持</v>
+        <v>n./v.</v>
       </c>
       <c r="D47" t="str">
-        <v>hold(保持)📢</v>
+        <v>混合</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>obvious</v>
       </c>
       <c r="B48" t="str">
-        <v>mix</v>
+        <v>/ˈɑːbviəs/</v>
       </c>
       <c r="C48" t="str">
-        <v>混合</v>
+        <v>adj.</v>
       </c>
       <c r="D48" t="str">
-        <v>mix(混合)📢</v>
+        <v>明显的</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>beard</v>
       </c>
       <c r="B49" t="str">
-        <v>obvious</v>
+        <v>/bɪrd/</v>
       </c>
       <c r="C49" t="str">
-        <v>明显的</v>
+        <v>n.</v>
       </c>
       <c r="D49" t="str">
-        <v>obvious(明显的)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>serious</v>
-      </c>
-      <c r="C50" t="str">
-        <v>严重的</v>
-      </c>
-      <c r="D50" t="str">
-        <v>serious(严重的)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>beard</v>
-      </c>
-      <c r="C51" t="str">
         <v>胡须</v>
-      </c>
-      <c r="D51" t="str">
-        <v>beard(胡须)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>sharp</v>
-      </c>
-      <c r="C52" t="str">
-        <v>敏锐</v>
-      </c>
-      <c r="D52" t="str">
-        <v>sharp(敏锐)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>possible</v>
-      </c>
-      <c r="C53" t="str">
-        <v>可能的</v>
-      </c>
-      <c r="D53" t="str">
-        <v>possible(可能的)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>snow</v>
-      </c>
-      <c r="C54" t="str">
-        <v>雪</v>
-      </c>
-      <c r="D54" t="str">
-        <v>snow(雪)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>camera</v>
-      </c>
-      <c r="C55" t="str">
-        <v>摄像头</v>
-      </c>
-      <c r="D55" t="str">
-        <v>camera(摄像头)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D49"/>
   </ignoredErrors>
 </worksheet>
 </file>